--- a/survey_templates/037_project_execution_readiness_survey--survey_templates.xlsx
+++ b/survey_templates/037_project_execution_readiness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_scope</t>
+          <t>project_scope_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Scope</t>
+          <t>Project Scope 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_team</t>
+          <t>project_team_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Team</t>
+          <t>Project Team 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>communication_plan</t>
+          <t>communication_plan_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Communication Plan</t>
+          <t>Communication Plan 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>issue</t>
+          <t>issue_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Issue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_phases</t>
+          <t>project_phases_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Project Phases</t>
+          <t>Project Phases 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1009,9 +1009,9 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1277,63 +1277,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>project_team_choices</t>
+          <t>project_team_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>project_team_choices</t>
+          <t>project_team_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>project_team_choices</t>
+          <t>project_team_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1481,165 +1481,165 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>issue_choices</t>
+          <t>issue_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>issue_choices</t>
+          <t>issue_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>issue_choices</t>
+          <t>issue_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>project_phases_choices</t>
+          <t>project_phases_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>project_phases_choices</t>
+          <t>project_phases_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>project_phases_choices</t>
+          <t>project_phases_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
